--- a/results/final_N33_v5/Trend_Method_Comparison/Excel/Master/TFPW_Audit.xlsx
+++ b/results/final_N33_v5/Trend_Method_Comparison/Excel/Master/TFPW_Audit.xlsx
@@ -551,7 +551,7 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1.029127931652926</v>
+        <v>2.725068</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>33.03768069475208</v>
+        <v>12.48</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>-1.8679</v>
@@ -785,7 +785,7 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1.029127931652926</v>
+        <v>2.725068</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>33.03768069475208</v>
+        <v>12.48</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>-1.8679</v>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1.032119481455827</v>
+        <v>1.677263</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>32.94192253017283</v>
+        <v>20.27</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>-2.1051</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1.033311336075184</v>
+        <v>1.706922</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>32.90392625434833</v>
+        <v>19.92</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>-2.1644</v>
@@ -1187,7 +1187,7 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="F2" s="7" t="n">
-        <v>1.029127931652926</v>
+        <v>2.725068</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>33.03768069475208</v>
+        <v>12.48</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>-1.8679</v>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1.032119481455827</v>
+        <v>1.677263</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>32.94192253017283</v>
+        <v>20.27</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>-2.1051</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="F4" s="7" t="n">
-        <v>1.033311336075184</v>
+        <v>1.706922</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>32.90392625434833</v>
+        <v>19.92</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>-2.1644</v>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1.032126695881812</v>
+        <v>1</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>31.9728189685143</v>
+        <v>33</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>2.1537</v>
@@ -1673,7 +1673,7 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="F2" s="9" t="n">
-        <v>1.029127931652926</v>
+        <v>2.725068</v>
       </c>
       <c r="G2" s="9" t="n">
-        <v>33.03768069475208</v>
+        <v>12.48</v>
       </c>
       <c r="H2" s="9" t="n">
         <v>-1.8679</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1.032119481455827</v>
+        <v>1.677263</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>32.94192253017283</v>
+        <v>20.27</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>-2.1051</v>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="F4" s="9" t="n">
-        <v>1.033311336075184</v>
+        <v>1.706922</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>32.90392625434833</v>
+        <v>19.92</v>
       </c>
       <c r="H4" s="9" t="n">
         <v>-2.1644</v>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1.032126695881812</v>
+        <v>1</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>31.9728189685143</v>
+        <v>33</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>2.1537</v>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>0.3971</v>
